--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_358_R36.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_358_R36.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7768</v>
+        <v>2.5696</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8126</v>
+        <v>3.9751</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0357</v>
+        <v>-1.4054</v>
       </c>
       <c r="G2" t="n">
         <v>2.2033</v>
@@ -610,13 +610,13 @@
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0221</v>
+        <v>0.8149</v>
       </c>
       <c r="T2" t="n">
-        <v>1.585</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4371</v>
+        <v>0.0674</v>
       </c>
       <c r="V2" t="n">
         <v>-1.6083</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.585</v>
+        <v>2.3902</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7952</v>
+        <v>1.634</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7897</v>
+        <v>0.7561</v>
       </c>
       <c r="G3" t="n">
         <v>1.8961</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.329</v>
+        <v>-0.5239</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2636</v>
+        <v>0.1024</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5926</v>
+        <v>-0.6262</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1418</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1227</v>
+        <v>1.9092</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4115</v>
+        <v>1.3996</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.5095</v>
       </c>
       <c r="G4" t="n">
         <v>-0.7457</v>
@@ -766,13 +766,13 @@
         <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2627</v>
+        <v>0.0492</v>
       </c>
       <c r="T4" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0751</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1757</v>
+        <v>-0.0259</v>
       </c>
       <c r="V4" t="n">
         <v>1.214</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>M. LO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.143</v>
+        <v>1.3137</v>
       </c>
       <c r="E5" t="n">
-        <v>1.109</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.034</v>
+        <v>1.234</v>
       </c>
       <c r="G5" t="n">
-        <v>0.026</v>
+        <v>-0.219</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0108</v>
+        <v>-0.5536</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0368</v>
+        <v>0.3346</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0368</v>
+        <v>-0.4369</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-0.5105</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0368</v>
+        <v>0.0736</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0108</v>
+        <v>0.2179</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0108</v>
+        <v>-0.0431</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.261</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0448</v>
+        <v>-0.3951</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.0196</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0448</v>
+        <v>-0.3756</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. LO</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0868</v>
+        <v>1.2102</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3489</v>
+        <v>1.109</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4356</v>
+        <v>0.1012</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.219</v>
+        <v>0.026</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5536</v>
+        <v>-0.0108</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3346</v>
+        <v>0.0368</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4369</v>
+        <v>0.0368</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5105</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0736</v>
+        <v>0.0368</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2179</v>
+        <v>-0.0108</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0431</v>
+        <v>-0.0108</v>
       </c>
       <c r="O6" t="n">
-        <v>0.261</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.622</v>
+        <v>0.112</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4481</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.174</v>
+        <v>0.112</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0762</v>
+        <v>0.5925</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1859</v>
+        <v>-0.6696</v>
       </c>
       <c r="F7" t="n">
         <v>1.2621</v>
@@ -1000,10 +1000,10 @@
         <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9436</v>
+        <v>0.4599</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8259</v>
+        <v>0.3422</v>
       </c>
       <c r="U7" t="n">
         <v>0.1177</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0776</v>
+        <v>0.2666</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3676</v>
+        <v>0.6782</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4452</v>
+        <v>-0.4116</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0842</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6893</v>
+        <v>-0.3451</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1415</v>
+        <v>0.1691</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5478</v>
+        <v>-0.5142</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>I. BRAZDEIKIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1813</v>
+        <v>-1.1819</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2179</v>
+        <v>-1.7435</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0366</v>
+        <v>0.5615</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0123</v>
+        <v>-0.2744</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2198</v>
+        <v>-0.6459</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2075</v>
+        <v>0.3714</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.49</v>
+        <v>-0.6388</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4398</v>
+        <v>-0.7492</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0502</v>
+        <v>0.1104</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5222</v>
+        <v>0.3644</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.78</v>
+        <v>0.1034</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2578</v>
+        <v>0.261</v>
       </c>
       <c r="P9" t="n">
-        <v>0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1485</v>
+        <v>-0.3018</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6844</v>
+        <v>0.0551</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8329</v>
+        <v>-0.3569</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2525</v>
+        <v>-0.1418</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.2525</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. BRAZDEIKIS</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6441</v>
+        <v>-1.2589</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.172</v>
+        <v>-1.4971</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5279</v>
+        <v>0.2382</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2744</v>
+        <v>-1.0123</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6459</v>
+        <v>-1.2198</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3714</v>
+        <v>0.2075</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6388</v>
+        <v>-0.49</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7492</v>
+        <v>-0.4398</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1104</v>
+        <v>-0.0502</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3644</v>
+        <v>-0.5222</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1034</v>
+        <v>-0.78</v>
       </c>
       <c r="O10" t="n">
-        <v>0.261</v>
+        <v>0.2578</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7639</v>
+        <v>-0.226</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3734</v>
+        <v>0.4052</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3905</v>
+        <v>-0.6313</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1418</v>
+        <v>-0.2525</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.2525</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.7631</v>
+        <v>-7.5625</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.409000000000001</v>
+        <v>-7.4772</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3542</v>
+        <v>-0.0853</v>
       </c>
       <c r="G11" t="n">
         <v>-5.742</v>
@@ -1312,13 +1312,13 @@
         <v>2.0876</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1808</v>
+        <v>0.0198</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4936</v>
+        <v>-0.5619</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3128</v>
+        <v>0.5816</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6083</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.4076</v>
+        <v>-9.0383</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.870200000000001</v>
+        <v>-8.7026</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5373</v>
+        <v>-0.3357</v>
       </c>
       <c r="G12" t="n">
         <v>-3.6661</v>
@@ -1390,13 +1390,13 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4066</v>
+        <v>-0.0373</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2617</v>
+        <v>-0.094</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.145</v>
+        <v>0.0567</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.2832</v>
+        <v>-8.7896</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.708</v>
+        <v>-11.2144</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4247</v>
+        <v>2.4246</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.3466</v>
+        <v>-9.346599999999999</v>
       </c>
       <c r="H13" t="n">
         <v>-4.0935</v>
@@ -1441,13 +1441,13 @@
         <v>-5.2532</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.142499999999999</v>
+        <v>-1.1425</v>
       </c>
       <c r="K13" t="n">
         <v>-2.229</v>
       </c>
       <c r="L13" t="n">
-        <v>1.086600000000001</v>
+        <v>1.086599999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-8.2041</v>
@@ -1456,10 +1456,10 @@
         <v>-1.8642</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.3398</v>
+        <v>-6.339799999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>9.999999999887876e-05</v>
+        <v>9.999999999976694e-05</v>
       </c>
       <c r="Q13" t="n">
         <v>-15.077</v>
@@ -1468,16 +1468,16 @@
         <v>15.0771</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8669</v>
+        <v>-0.3734000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2724000000000002</v>
+        <v>1.2211</v>
       </c>
       <c r="U13" t="n">
         <v>-1.5947</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9304000000000003</v>
+        <v>0.9303999999999999</v>
       </c>
       <c r="W13" t="n">
         <v>3.7838</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. CABOCLO</t>
+          <t>J. ANDERSON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8839</v>
+        <v>5.744</v>
       </c>
       <c r="E14" t="n">
-        <v>7.7453</v>
+        <v>2.1573</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.8614</v>
+        <v>3.5867</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6672</v>
+        <v>3.571</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1524</v>
+        <v>2.1789</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4851</v>
+        <v>1.3921</v>
       </c>
       <c r="J14" t="n">
-        <v>3.0713</v>
+        <v>2.9313</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9241</v>
+        <v>1.5327</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1472</v>
+        <v>1.3986</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.404</v>
+        <v>0.6397</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2283</v>
+        <v>0.6462</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6323</v>
+        <v>-0.0065</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9278</v>
+        <v>2.7834</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3199</v>
+        <v>0.5493</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9935</v>
+        <v>0.3857</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3264</v>
+        <v>0.1637</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.031</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.6805</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.7115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. ANDERSON</t>
+          <t>B. CABOCLO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.6203</v>
+        <v>4.823</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1573</v>
+        <v>6.9197</v>
       </c>
       <c r="F15" t="n">
-        <v>3.4631</v>
+        <v>-2.0966</v>
       </c>
       <c r="G15" t="n">
-        <v>3.571</v>
+        <v>2.6672</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1789</v>
+        <v>3.1524</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3921</v>
+        <v>-0.4851</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9313</v>
+        <v>3.0713</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5327</v>
+        <v>2.9241</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3986</v>
+        <v>0.1472</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6397</v>
+        <v>-0.404</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6462</v>
+        <v>0.2283</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0065</v>
+        <v>-0.6323</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7834</v>
+        <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4257</v>
+        <v>1.259</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3857</v>
+        <v>1.1679</v>
       </c>
       <c r="U15" t="n">
-        <v>0.04</v>
+        <v>0.0912</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.031</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.6805</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-2.7115</v>
       </c>
     </row>
     <row r="16">
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2225</v>
+        <v>3.1661</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2532</v>
+        <v>1.1968</v>
       </c>
       <c r="F16" t="n">
         <v>1.9693</v>
@@ -1702,10 +1702,10 @@
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2082</v>
+        <v>1.1518</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2908</v>
+        <v>0.6528</v>
       </c>
       <c r="U16" t="n">
         <v>0.4991</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2863</v>
+        <v>0.8195</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0471</v>
+        <v>-0.7786</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2392</v>
+        <v>1.5981</v>
       </c>
       <c r="G17" t="n">
         <v>0.8911</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2311</v>
+        <v>-0.6978</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6765</v>
+        <v>-0.1491</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9076</v>
+        <v>-0.5487</v>
       </c>
       <c r="V17" t="n">
         <v>0.3943</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ABASS</t>
+          <t>D. BERTANS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2028</v>
+        <v>0.2739</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2694</v>
+        <v>0.6967</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4722</v>
+        <v>-0.4228</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7441</v>
+        <v>1.3642</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7838000000000001</v>
+        <v>0.287</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9603</v>
+        <v>1.0773</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.4687</v>
+        <v>1.6322</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7191</v>
+        <v>-0.131</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7495000000000001</v>
+        <v>1.7631</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2755</v>
+        <v>-0.2679</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.4179</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2108</v>
+        <v>-0.6859</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2511</v>
+        <v>0.5179</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1993</v>
+        <v>0.2243</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0518</v>
+        <v>0.2937</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>M. WRIGHT IV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1851</v>
+        <v>0.0682</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.0758</v>
+        <v>-2.4251</v>
       </c>
       <c r="F19" t="n">
-        <v>3.8908</v>
+        <v>2.4934</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3451</v>
+        <v>1.2045</v>
       </c>
       <c r="H19" t="n">
-        <v>0.097</v>
+        <v>1.007</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2481</v>
+        <v>0.1975</v>
       </c>
       <c r="J19" t="n">
-        <v>0.008399999999999999</v>
+        <v>1.1009</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4566</v>
+        <v>0.6862</v>
       </c>
       <c r="L19" t="n">
-        <v>0.465</v>
+        <v>0.4148</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3367</v>
+        <v>0.1036</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5536</v>
+        <v>0.3209</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7831</v>
+        <v>-0.2173</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.8556</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q19" t="n">
         <v>-3.4793</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6237</v>
+        <v>2.5515</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1836</v>
+        <v>-0.2084</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7468</v>
+        <v>-0.0468</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9304</v>
+        <v>-0.1617</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. BERTANS</t>
+          <t>A. ABASS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4167</v>
+        <v>-0.3032</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1069</v>
+        <v>-0.9771</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5236</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>1.3642</v>
+        <v>-1.7441</v>
       </c>
       <c r="H20" t="n">
-        <v>0.287</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0773</v>
+        <v>-0.9603</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6322</v>
+        <v>-1.4687</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.131</v>
+        <v>-0.7191</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7631</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2679</v>
+        <v>-0.2755</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4179</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6859</v>
+        <v>-0.2108</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1726</v>
+        <v>0.7451</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3655</v>
+        <v>0.4916</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1929</v>
+        <v>0.2535</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. PREPELIC</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4336</v>
+        <v>-0.3296</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3091</v>
+        <v>-3.8399</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8754999999999999</v>
+        <v>3.5104</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3145</v>
+        <v>1.3451</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3145</v>
+        <v>0.097</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1.2481</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>-0.4566</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.465</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3145</v>
+        <v>1.3367</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3145</v>
+        <v>0.5536</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.7831</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6959</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0523</v>
+        <v>0.0391</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1494</v>
+        <v>-0.5109</v>
       </c>
       <c r="U21" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. WRIGHT IV</t>
+          <t>K. PREPELIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5773</v>
+        <v>-0.4</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.779</v>
+        <v>-1.3091</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2017</v>
+        <v>0.9091</v>
       </c>
       <c r="G22" t="n">
-        <v>1.2045</v>
+        <v>0.3145</v>
       </c>
       <c r="H22" t="n">
-        <v>1.007</v>
+        <v>0.3145</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1975</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1009</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6862</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4148</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1036</v>
+        <v>0.3145</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3209</v>
+        <v>0.3145</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2173</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9278</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>2.5515</v>
+        <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.854</v>
+        <v>-0.0187</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4007</v>
+        <v>-0.1494</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4533</v>
+        <v>0.1307</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.274</v>
+        <v>-1.156</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0337</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="F23" t="n">
         <v>-0.2402</v>
@@ -2248,10 +2248,10 @@
         <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0459</v>
+        <v>-1.6363</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1256</v>
+        <v>-3.0077</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0797</v>
+        <v>1.3714</v>
       </c>
       <c r="G24" t="n">
         <v>-1.597</v>
@@ -2326,13 +2326,13 @@
         <v>1.6237</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9129</v>
+        <v>-0.5032</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4086</v>
+        <v>-0.2906</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5043</v>
+        <v>-0.2126</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>10.2832</v>
+        <v>11.0696</v>
       </c>
       <c r="E25" t="n">
         <v>-2.2828</v>
       </c>
       <c r="F25" t="n">
-        <v>12.5663</v>
+        <v>13.3527</v>
       </c>
       <c r="G25" t="n">
         <v>9.3466</v>
@@ -2404,13 +2404,13 @@
         <v>15.077</v>
       </c>
       <c r="S25" t="n">
-        <v>1.8669</v>
+        <v>2.6533</v>
       </c>
       <c r="T25" t="n">
-        <v>1.594499999999999</v>
+        <v>1.5947</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2725</v>
+        <v>1.0589</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9303000000000001</v>
